--- a/service_model_training_data_template.xlsx
+++ b/service_model_training_data_template.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Training_Data'!$A$2:$F$30</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,77 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B4FA0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F1FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0E8F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3E5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -105,139 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="medium">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -603,788 +413,523 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>intent</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="F1" s="12" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="n"/>
-      <c r="B2" s="13" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Japanese</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Japanese</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>How do I reset my password?</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>パスワードをリセットしたい</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>To reset: Settings &gt; Account &gt; Reset Password. Check email for link (30 min expiry).</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>リセットするには：設定 &gt; アカウント &gt; パスワードリセット。メールにリンクが届きます（30分有効）。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>I forgot my password</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>パスワードを忘れました</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Can't log in to my account</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>ログインできません</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>my pasword doesnt work</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>パスワードを変更したい</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>locked out of account</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>アカウントにアクセスできない</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>How can I recover my account?</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>パスワードがわからない</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>account_password</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>password reset please</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>subscription_cancel</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>How do I cancel my subscription?</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>サブスクリプションをキャンセルしたい</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>To cancel: Settings &gt; Subscription &gt; Cancel Plan. Access continues until billing period ends.</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>キャンセル：設定 &gt; サブスクリプション &gt; キャンセル。請求期間の終了までアクセス継続。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>subscription_cancel</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>I want to unsubscribe</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>解約したい</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>subscription_cancel</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>cancel my plan</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>退会方法を教えてください</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>subscription_cancel</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>stop charging me</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>課金を止めてください</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>billing_question</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Why was I charged twice?</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>二重に請求されたのはなぜ？</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Check Settings &gt; Billing for payment history. Unexpected charges may be from plan upgrade.</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>設定 &gt; 請求からお支払い履歴をご確認ください。予期しない請求はアップグレードの可能性があります。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>billing_question</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>I need a receipt</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>領収書がほしい</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>billing_question</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>How do I update payment method?</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>支払い方法を変更したい</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>feature_howto</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>How do I use dark mode?</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>ダークモードの使い方</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Enable dark mode: Settings &gt; Display &gt; Dark Mode. Changes apply immediately.</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>ダークモード：設定 &gt; 表示 &gt; ダークモード。即座に反映されます。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>feature_howto</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Where are my saved items?</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>保存したアイテムはどこ？</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>bug_report</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>The app keeps crashing</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>アプリが落ちる</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Sorry about that! Please submit a bug report with your device model and app version.</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>ご不便をおかけして申し訳ございません。デバイスモデルとアプリバージョンを添えてご報告ください。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>bug_report</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>I found a bug</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>バグを見つけました</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>bug_report</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>app is broken</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>アプリが動かない</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>bug_report</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>something is not working</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>正常に動作しません</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>need_human</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>I want to talk to a real person</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>人間と話したい</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Please fill out our support form. We'll respond within 24 hours.</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>サポートフォームにご記入ください。24時間以内にご連絡いたします。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>need_human</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Connect me to customer support</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>サポートに繋いでください</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>need_human</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>I need human help</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>直接相談したい</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>reject</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>What's the weather today?</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>今日の天気は？</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>I can only help with [AppName] questions. Is there anything about the app I can help with?</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>[AppName]に関するご質問のみお答えできます。アプリについてお手伝いできることはありますか？</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>reject</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Tell me a joke</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>冗談を教えて</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>reject</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>What time is it?</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>今何時？</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>reject</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Who won the game?</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>昨日の試合の結果は？</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>reject</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Can you order me pizza?</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>ピザを注文して</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1646,20 +1191,1815 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>I can't remember my password</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>パスワードが思い出せない</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>How to change my login password?</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ログインパスワードの変更方法は？</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Reset password not working</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>パスワードリセットがうまくいかない</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>I need to update my password</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>パスワードを更新したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Where do I change my password?</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>パスワードはどこで変更できますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>My password expired</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>パスワードの有効期限が切れました</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Account locked after wrong password</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>パスワードを間違えてロックされた</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>I keep getting password error</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>パスワードエラーが出続けます</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Help me get back into my account</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>アカウントに戻れるようにして</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Change login info</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ログイン情報を変更したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Forgot my credentials</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>認証情報を忘れました</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>How to set a new password</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>新しいパスワードを設定するには</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>I want to stop paying for the service</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>サービスの支払いを止めたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>How to end my membership?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>会員を解約するには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cancel my account subscription</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>アカウントのサブスクをキャンセルしたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>I don't want to renew</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>更新したくありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Stop my monthly payment</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>月額課金を止めてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Where can I cancel my plan?</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>プランのキャンセルはどこで？</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>I want to downgrade to free</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>無料プランに戻したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>End my premium subscription</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>プレミアムの登録を終了したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Remove my subscription</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>サブスクリプションを解除したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>I no longer need this service</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>このサービスはもう不要です</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Unsubscribe me from everything</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>すべての登録を解除して</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>subscription</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cancel renewal please</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>更新をキャンセルしてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>I see an unexpected charge</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>予期しない請求があります</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Where can I view my invoices?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>請求書はどこで確認できますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>I was overcharged</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>過剰請求されました</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>When is my next billing date?</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>次の請求日はいつですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Can I get a refund?</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>返金してもらえますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>How to switch to annual billing?</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>年間払いに変更するには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>My credit card was declined</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>クレジットカードが拒否されました</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>How much does the premium plan cost?</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>プレミアムプランはいくらですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>I want to change my billing address</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>請求先住所を変更したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Payment failed but money was taken</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>支払い失敗なのにお金が引かれた</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>How to apply a promo code?</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>プロモーションコードの適用方法は？</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>billing</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>I need an itemized receipt</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>明細付きの領収書が必要です</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>How do I enable notifications?</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>通知を有効にするには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Where are the settings?</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>設定はどこですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>How to export my data?</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>データをエクスポートするには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Can I use offline mode?</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>オフラインモードは使えますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>How to change language?</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>言語を変更するには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>How to share my profile?</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>プロフィールを共有するには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Is there a search function?</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>検索機能はありますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>How do I delete my history?</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>履歴を削除するには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Can I sync across devices?</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>デバイス間で同期できますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>How to set up two-factor auth?</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>二段階認証の設定方法は？</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>How to customize my dashboard?</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ダッシュボードをカスタマイズするには？</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>howto</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Can I change my username?</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ユーザー名を変更できますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Screen goes blank in settings</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>設定を開くと画面が真っ白になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>App freezes on loading screen</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ロード画面でフリーズする</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>I keep getting error messages</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>エラーメッセージが出続けます</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>App crashes every time I log in</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ログインするたびにアプリが落ちる</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Buttons are not responding</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ボタンが反応しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Page doesn't load properly</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ページが正しく表示されない</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Lost my data after the update</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>アップデート後にデータが消えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>There's a display glitch</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>表示にバグがあります</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Notifications stopped working</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>通知が届かなくなった</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Search returns wrong results</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>検索結果がおかしい</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Video won't play in the app</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>アプリで動画が再生されない</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Error when I try to save</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>保存しようとするとエラーが出る</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Let me speak to a manager</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>マネージャーと話させてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>I want to file a complaint</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>苦情を申し立てたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>This bot can't help me</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>このボットでは解決できません</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Transfer me to a human agent</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>人間のオペレーターに転送して</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>I need to talk to someone real</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>本物の人と話す必要があります</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Can I call customer service?</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>カスタマーサービスに電話できますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>I want a phone call back</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>折り返し電話がほしい</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Please escalate my issue</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>問題をエスカレートしてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Is there a live chat option?</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ライブチャットはありますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>My problem is too complicated</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ボットでは対応できない問題です</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Get me a real support agent</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>実際のスタッフにつないでください</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>I need personalized help</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>個別のサポートが必要です</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>What's the capital of France?</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>フランスの首都はどこ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Play some music</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>音楽を再生して</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>How's the stock market today?</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>今日の株式市場はどう？</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Write me an essay</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>エッセイを書いて</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Translate this to Spanish</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>これをスペイン語に翻訳して</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Book me a flight</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>飛行機を予約して</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>What's 2+2?</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2+2は？</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Set an alarm for 7am</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>午前7時にアラームをセットして</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Who is the president?</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>大統領は誰？</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Find me a restaurant nearby</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>近くのレストランを探して</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F30"/>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="B1:B2"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B172 B173 B174 B175 B176 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B201 B202 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B222 B223 B224 B225 B226 B227 B228 B229 B230 B231 B232 B233 B234 B235 B236 B237 B238 B239 B240 B241 B242 B243 B244 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B258 B259 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B276 B277 B278 B279 B280 B281 B282 B283 B284 B285 B286 B287 B288 B289 B290 B291 B292 B293 B294 B295 B296 B297 B298 B299 B300 B301 B302 B303 B304 B305 B306 B307 B308 B309 B310 B311 B312 B313 B314 B315 B316 B317 B318 B319 B320 B321 B322 B323 B324 B325 B326 B327 B328 B329 B330 B331 B332 B333 B334 B335 B336 B337 B338 B339 B340 B341 B342 B343 B344 B345 B346 B347 B348 B349 B350 B351 B352 B353 B354 B355 B356 B357 B358 B359 B360 B361 B362 B363 B364 B365 B366 B367 B368 B369 B370 B371 B372 B373 B374 B375 B376 B377 B378 B379 B380 B381 B382 B383 B384 B385 B386 B387 B388 B389 B390 B391 B392 B393 B394 B395 B396 B397 B398 B399 B400 B401 B402 B403 B404 B405 B406 B407 B408 B409 B410 B411 B412 B413 B414 B415 B416 B417 B418 B419 B420 B421 B422 B423 B424 B425 B426 B427 B428 B429 B430 B431 B432 B433 B434 B435 B436 B437 B438 B439 B440 B441 B442 B443 B444 B445 B446 B447 B448 B449 B450 B451 B452 B453 B454 B455 B456 B457 B458 B459 B460 B461 B462 B463 B464 B465 B466 B467 B468 B469 B470 B471 B472 B473 B474 B475 B476 B477 B478 B479 B480 B481 B482 B483 B484 B485 B486 B487 B488 B489 B490 B491 B492 B493 B494 B495 B496 B497 B498 B499 B500 B501 B502 B503 B504 B505 B506 B507 B508 B509 B510 B511 B512 B513 B514 B515 B516 B517 B518 B519 B520 B521 B522 B523 B524 B525 B526 B527 B528 B529 B530 B531 B532 B533 B534 B535 B536 B537 B538 B539 B540 B541 B542 B543 B544 B545 B546 B547 B548 B549 B550 B551 B552 B553 B554 B555 B556 B557 B558 B559 B560 B561 B562 B563 B564 B565 B566 B567 B568 B569 B570 B571 B572 B573 B574 B575 B576 B577 B578 B579 B580 B581 B582 B583 B584 B585 B586 B587 B588 B589 B590 B591 B592 B593 B594 B595 B596 B597 B598 B599 B600 B601 B602 B603 B604 B605 B606 B607 B608 B609 B610 B611 B612 B613 B614 B615 B616 B617 B618 B619 B620 B621 B622 B623 B624 B625 B626 B627 B628 B629 B630 B631 B632 B633 B634 B635 B636 B637 B638 B639 B640 B641 B642 B643 B644 B645 B646 B647 B648 B649 B650 B651 B652 B653 B654 B655 B656 B657 B658 B659 B660 B661 B662 B663 B664 B665 B666 B667 B668 B669 B670 B671 B672 B673 B674 B675 B676 B677 B678 B679 B680 B681 B682 B683 B684 B685 B686 B687 B688 B689 B690 B691 B692 B693 B694 B695 B696 B697 B698 B699 B700 B701 B702 B703 B704 B705 B706 B707 B708 B709 B710 B711 B712 B713 B714 B715 B716 B717 B718 B719 B720 B721 B722 B723 B724 B725 B726 B727 B728 B729 B730 B731 B732 B733 B734 B735 B736 B737 B738 B739 B740 B741 B742 B743 B744 B745 B746 B747 B748 B749 B750 B751 B752 B753 B754 B755 B756 B757 B758 B759 B760 B761 B762 B763 B764 B765 B766 B767 B768 B769 B770 B771 B772 B773 B774 B775 B776 B777 B778 B779 B780 B781 B782 B783 B784 B785 B786 B787 B788 B789 B790 B791 B792 B793 B794 B795 B796 B797 B798 B799 B800 B801 B802 B803 B804 B805 B806 B807 B808 B809 B810 B811 B812 B813 B814 B815 B816 B817 B818 B819 B820 B821 B822 B823 B824 B825 B826 B827 B828 B829 B830 B831 B832 B833 B834 B835 B836 B837 B838 B839 B840 B841 B842 B843 B844 B845 B846 B847 B848 B849 B850 B851 B852 B853 B854 B855 B856 B857 B858 B859 B860 B861 B862 B863 B864 B865 B866 B867 B868 B869 B870 B871 B872 B873 B874 B875 B876 B877 B878 B879 B880 B881 B882 B883 B884 B885 B886 B887 B888 B889 B890 B891 B892 B893 B894 B895 B896 B897 B898 B899 B900 B901 B902 B903 B904 B905 B906 B907 B908 B909 B910 B911 B912 B913 B914 B915 B916 B917 B918 B919 B920 B921 B922 B923 B924 B925 B926 B927 B928 B929 B930 B931 B932 B933 B934 B935 B936 B937 B938 B939 B940 B941 B942 B943 B944 B945 B946 B947 B948 B949 B950 B951 B952 B953 B954 B955 B956 B957 B958 B959 B960 B961 B962 B963 B964 B965 B966 B967 B968 B969 B970 B971 B972 B973 B974 B975 B976 B977 B978 B979 B980 B981 B982 B983 B984 B985 B986 B987 B988 B989 B990 B991 B992 B993 B994 B995 B996 B997 B998 B999 B1000 B1001 B1002 B1003 B1004 B1005 B1006 B1007 B1008 B1009 B1010 B1011 B1012 B1013 B1014 B1015 B1016 B1017 B1018 B1019 B1020 B1021 B1022 B1023 B1024 B1025 B1026 B1027 B1028 B1029 B1030 B1031 B1032 B1033 B1034 B1035 B1036 B1037 B1038 B1039 B1040 B1041 B1042 B1043 B1044 B1045 B1046 B1047 B1048 B1049 B1050 B1051 B1052 B1053 B1054 B1055 B1056 B1057 B1058 B1059 B1060 B1061 B1062 B1063 B1064 B1065 B1066 B1067 B1068 B1069 B1070 B1071 B1072 B1073 B1074 B1075 B1076 B1077 B1078 B1079 B1080 B1081 B1082 B1083 B1084 B1085 B1086 B1087 B1088 B1089 B1090 B1091 B1092 B1093 B1094 B1095 B1096 B1097 B1098 B1099 B1100 B1101 B1102 B1103 B1104 B1105 B1106 B1107 B1108 B1109 B1110 B1111 B1112 B1113 B1114 B1115 B1116 B1117 B1118 B1119 B1120 B1121 B1122 B1123 B1124 B1125 B1126 B1127 B1128 B1129 B1130 B1131 B1132 B1133 B1134 B1135 B1136 B1137 B1138 B1139 B1140 B1141 B1142 B1143 B1144 B1145 B1146 B1147 B1148 B1149 B1150 B1151 B1152 B1153 B1154 B1155 B1156 B1157 B1158 B1159 B1160 B1161 B1162 B1163 B1164 B1165 B1166 B1167 B1168 B1169 B1170 B1171 B1172 B1173 B1174 B1175 B1176 B1177 B1178 B1179 B1180 B1181 B1182 B1183 B1184 B1185 B1186 B1187 B1188 B1189 B1190 B1191 B1192 B1193 B1194 B1195 B1196 B1197 B1198 B1199 B1200 B1201 B1202 B1203 B1204 B1205 B1206 B1207 B1208 B1209 B1210 B1211 B1212 B1213 B1214 B1215 B1216 B1217 B1218 B1219 B1220 B1221 B1222 B1223 B1224 B1225 B1226 B1227 B1228 B1229 B1230 B1231 B1232 B1233 B1234 B1235 B1236 B1237 B1238 B1239 B1240 B1241 B1242 B1243 B1244 B1245 B1246 B1247 B1248 B1249 B1250 B1251 B1252 B1253 B1254 B1255 B1256 B1257 B1258 B1259 B1260 B1261 B1262 B1263 B1264 B1265 B1266 B1267 B1268 B1269 B1270 B1271 B1272 B1273 B1274 B1275 B1276 B1277 B1278 B1279 B1280 B1281 B1282 B1283 B1284 B1285 B1286 B1287 B1288 B1289 B1290 B1291 B1292 B1293 B1294 B1295 B1296 B1297 B1298 B1299 B1300 B1301 B1302 B1303 B1304 B1305 B1306 B1307 B1308 B1309 B1310 B1311 B1312 B1313 B1314 B1315 B1316 B1317 B1318 B1319 B1320 B1321 B1322 B1323 B1324 B1325 B1326 B1327 B1328 B1329 B1330 B1331 B1332 B1333 B1334 B1335 B1336 B1337 B1338 B1339 B1340 B1341 B1342 B1343 B1344 B1345 B1346 B1347 B1348 B1349 B1350 B1351 B1352 B1353 B1354 B1355 B1356 B1357 B1358 B1359 B1360 B1361 B1362 B1363 B1364 B1365 B1366 B1367 B1368 B1369 B1370 B1371 B1372 B1373 B1374 B1375 B1376 B1377 B1378 B1379 B1380 B1381 B1382 B1383 B1384 B1385 B1386 B1387 B1388 B1389 B1390 B1391 B1392 B1393 B1394 B1395 B1396 B1397 B1398 B1399 B1400 B1401 B1402 B1403 B1404 B1405 B1406 B1407 B1408 B1409 B1410 B1411 B1412 B1413 B1414 B1415 B1416 B1417 B1418 B1419 B1420 B1421 B1422 B1423 B1424 B1425 B1426 B1427 B1428 B1429 B1430 B1431 B1432 B1433 B1434 B1435 B1436 B1437 B1438 B1439 B1440 B1441 B1442 B1443 B1444 B1445 B1446 B1447 B1448 B1449 B1450 B1451 B1452 B1453 B1454 B1455 B1456 B1457 B1458 B1459 B1460 B1461 B1462 B1463 B1464 B1465 B1466 B1467 B1468 B1469 B1470 B1471 B1472 B1473 B1474 B1475 B1476 B1477 B1478 B1479 B1480 B1481 B1482 B1483 B1484 B1485 B1486 B1487 B1488 B1489 B1490 B1491 B1492 B1493 B1494 B1495 B1496 B1497 B1498 B1499 B1500 B1501 B1502 B1503 B1504 B1505 B1506 B1507 B1508 B1509 B1510 B1511 B1512 B1513 B1514 B1515 B1516 B1517 B1518 B1519 B1520 B1521 B1522 B1523 B1524 B1525 B1526 B1527 B1528 B1529 B1530 B1531 B1532 B1533 B1534 B1535 B1536 B1537 B1538 B1539 B1540 B1541 B1542 B1543 B1544 B1545 B1546 B1547 B1548 B1549 B1550 B1551 B1552 B1553 B1554 B1555 B1556 B1557 B1558 B1559 B1560 B1561 B1562 B1563 B1564 B1565 B1566 B1567 B1568 B1569 B1570 B1571 B1572 B1573 B1574 B1575 B1576 B1577 B1578 B1579 B1580 B1581 B1582 B1583 B1584 B1585 B1586 B1587 B1588 B1589 B1590 B1591 B1592 B1593 B1594 B1595 B1596 B1597 B1598 B1599 B1600 B1601 B1602 B1603 B1604 B1605 B1606 B1607 B1608 B1609 B1610 B1611 B1612 B1613 B1614 B1615 B1616 B1617 B1618 B1619 B1620 B1621 B1622 B1623 B1624 B1625 B1626 B1627 B1628 B1629 B1630 B1631 B1632 B1633 B1634 B1635 B1636 B1637 B1638 B1639 B1640 B1641 B1642 B1643 B1644 B1645 B1646 B1647 B1648 B1649 B1650 B1651 B1652 B1653 B1654 B1655 B1656 B1657 B1658 B1659 B1660 B1661 B1662 B1663 B1664 B1665 B1666 B1667 B1668 B1669 B1670 B1671 B1672 B1673 B1674 B1675 B1676 B1677 B1678 B1679 B1680 B1681 B1682 B1683 B1684 B1685 B1686 B1687 B1688 B1689 B1690 B1691 B1692 B1693 B1694 B1695 B1696 B1697 B1698 B1699 B1700 B1701 B1702 B1703 B1704 B1705 B1706 B1707 B1708 B1709 B1710 B1711 B1712 B1713 B1714 B1715 B1716 B1717 B1718 B1719 B1720 B1721 B1722 B1723 B1724 B1725 B1726 B1727 B1728 B1729 B1730 B1731 B1732 B1733 B1734 B1735 B1736 B1737 B1738 B1739 B1740 B1741 B1742 B1743 B1744 B1745 B1746 B1747 B1748 B1749 B1750 B1751 B1752 B1753 B1754 B1755 B1756 B1757 B1758 B1759 B1760 B1761 B1762 B1763 B1764 B1765 B1766 B1767 B1768 B1769 B1770 B1771 B1772 B1773 B1774 B1775 B1776 B1777 B1778 B1779 B1780 B1781 B1782 B1783 B1784 B1785 B1786 B1787 B1788 B1789 B1790 B1791 B1792 B1793 B1794 B1795 B1796 B1797 B1798 B1799 B1800 B1801 B1802 B1803 B1804 B1805 B1806 B1807 B1808 B1809 B1810 B1811 B1812 B1813 B1814 B1815 B1816 B1817 B1818 B1819 B1820 B1821 B1822 B1823 B1824 B1825 B1826 B1827 B1828 B1829 B1830 B1831 B1832 B1833 B1834 B1835 B1836 B1837 B1838 B1839 B1840 B1841 B1842 B1843 B1844 B1845 B1846 B1847 B1848 B1849 B1850 B1851 B1852 B1853 B1854 B1855 B1856 B1857 B1858 B1859 B1860 B1861 B1862 B1863 B1864 B1865 B1866 B1867 B1868 B1869 B1870 B1871 B1872 B1873 B1874 B1875 B1876 B1877 B1878 B1879 B1880 B1881 B1882 B1883 B1884 B1885 B1886 B1887 B1888 B1889 B1890 B1891 B1892 B1893 B1894 B1895 B1896 B1897 B1898 B1899 B1900 B1901 B1902 B1903 B1904 B1905 B1906 B1907 B1908 B1909 B1910 B1911 B1912 B1913 B1914 B1915 B1916 B1917 B1918 B1919 B1920 B1921 B1922 B1923 B1924 B1925 B1926 B1927 B1928 B1929 B1930 B1931 B1932 B1933 B1934 B1935 B1936 B1937 B1938 B1939 B1940 B1941 B1942 B1943 B1944 B1945 B1946 B1947 B1948 B1949 B1950 B1951 B1952 B1953 B1954 B1955 B1956 B1957 B1958 B1959 B1960 B1961 B1962 B1963 B1964 B1965 B1966 B1967 B1968 B1969 B1970 B1971 B1972 B1973 B1974 B1975 B1976 B1977 B1978 B1979 B1980 B1981 B1982 B1983 B1984 B1985 B1986 B1987 B1988 B1989 B1990 B1991 B1992 B1993 B1994 B1995 B1996 B1997 B1998 B1999" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid type" error="answer = direct reply&#10;support = show support form&#10;reject = out of scope" type="list">
-      <formula1>"answer,support,reject"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/service_model_training_data_template.xlsx
+++ b/service_model_training_data_template.xlsx
@@ -503,6 +503,16 @@
           <t>パスワードを忘れました</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No worries! Tap 'Forgot Password' on the login screen, enter your email, and we'll send a reset link within 1 minute.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ご安心ください！ログイン画面の「パスワードを忘れた」をタップし、メールアドレスを入力してください。1分以内にリセットリンクをお送りします。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
@@ -515,6 +525,16 @@
           <t>ログインできません</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Let's get you back in! First try resetting your password via Settings &gt; Account &gt; Reset Password. If that doesn't work, check if your account email is correct.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>アカウントに戻れるようお手伝いします！まず設定 &gt; アカウント &gt; パスワードリセットをお試しください。それでもダメな場合は、メールアドレスが正しいかご確認ください。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -527,6 +547,16 @@
           <t>パスワードを変更したい</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Your password may have expired or been changed. Try the 'Forgot Password' option on the login screen to create a new one.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>パスワードの有効期限が切れているか、変更された可能性があります。ログイン画面の「パスワードを忘れた」から新しいパスワードを作成してください。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -539,6 +569,16 @@
           <t>アカウントにアクセスできない</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Account lockouts happen after too many failed attempts. Wait 15 minutes and try again, or reset your password via email to unlock immediately.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ログイン試行回数が多すぎるとアカウントがロックされます。15分待ってから再試行するか、メールでパスワードをリセットして即座にロック解除できます。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -551,6 +591,16 @@
           <t>パスワードがわからない</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>To recover your account: go to the login screen &gt; tap 'Forgot Password' &gt; enter your registered email. A recovery link will be sent within minutes.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>アカウントを復旧するには：ログイン画面 &gt; 「パスワードを忘れた」をタップ &gt; 登録メールアドレスを入力。数分以内に復旧リンクが届きます。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
@@ -558,6 +608,16 @@
           <t>password reset please</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Absolutely! Go to Settings &gt; Account &gt; Reset Password. We'll send a secure link to your email right away.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>もちろんです！設定 &gt; アカウント &gt; パスワードリセットへ進んでください。メールにリンクをすぐにお送りします。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -602,6 +662,16 @@
           <t>解約したい</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>To unsubscribe: Settings &gt; Subscription &gt; Cancel Plan. Your access continues until the current billing cycle ends.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>解約するには：設定 &gt; サブスクリプション &gt; キャンセル。現在の請求期間が終わるまでアクセスは継続されます。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
@@ -614,6 +684,16 @@
           <t>退会方法を教えてください</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>To cancel your plan: Settings &gt; Subscription &gt; Cancel Plan. No immediate cutoff — you'll keep access until your current period ends.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>プランのキャンセル：設定 &gt; サブスクリプション &gt; キャンセル。すぐに停止されることはなく、現在の期間終了までご利用いただけます。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="C13" t="inlineStr">
@@ -626,6 +706,16 @@
           <t>課金を止めてください</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>To stop charges: go to Settings &gt; Subscription &gt; Cancel Plan. Future charges will stop, and you keep access until the period ends.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>課金を停止するには：設定 &gt; サブスクリプション &gt; キャンセル。今後の課金は停止され、期間終了までアクセスは継続されます。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -670,6 +760,16 @@
           <t>領収書がほしい</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>You can download receipts from Settings &gt; Billing &gt; Invoice History. Each transaction has a downloadable PDF receipt.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>領収書は設定 &gt; 請求 &gt; 請求履歴からダウンロードできます。各取引にPDF領収書があります。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
@@ -682,6 +782,16 @@
           <t>支払い方法を変更したい</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>To update payment method: Settings &gt; Billing &gt; Payment Methods &gt; Add/Edit. You can add credit cards, debit cards, or PayPal.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>支払い方法の更新：設定 &gt; 請求 &gt; 支払い方法 &gt; 追加/編集。クレジットカード、デビットカード、PayPalを追加できます。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -726,6 +836,16 @@
           <t>保存したアイテムはどこ？</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Your saved items are at: Home &gt; Saved tab (bookmark icon). You can also search within saved items.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>保存したアイテムは：ホーム &gt; 保存タブ（ブックマークアイコン）にあります。保存アイテム内での検索も可能です。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -770,6 +890,16 @@
           <t>バグを見つけました</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Thanks for reporting! Please describe the bug at Settings &gt; Help &gt; Report a Bug. Include screenshots if possible — it helps us fix it faster.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ご報告ありがとうございます！設定 &gt; ヘルプ &gt; バグを報告 で詳細をお知らせください。スクリーンショットがあると早く修正できます。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -782,6 +912,16 @@
           <t>アプリが動かない</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sorry to hear that! Try these first: 1) Force close and reopen 2) Update the app 3) Restart your device. If it persists, report at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>申し訳ございません！まずお試しください：1) 強制終了して再起動 2) アプリを更新 3) デバイスを再起動。改善しない場合は設定 &gt; ヘルプ &gt; バグを報告からご連絡ください。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
@@ -794,6 +934,16 @@
           <t>正常に動作しません</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sorry about that! Can you tell us what's not working? In the meantime, try updating the app and restarting your device. Report details at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ご不便をおかけして申し訳ございません！何が動作していないかお知らせください。アプリの更新とデバイスの再起動もお試しください。詳細は設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -838,6 +988,16 @@
           <t>サポートに繋いでください</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>I'll connect you now! Please fill out our support form at Settings &gt; Help &gt; Contact Support. A team member will respond within 24 hours.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>すぐにおつなぎします！設定 &gt; ヘルプ &gt; サポートに連絡のフォームにご記入ください。24時間以内にチームメンバーが対応します。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="C25" t="inlineStr">
@@ -850,6 +1010,16 @@
           <t>直接相談したい</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Absolutely! Our support team is ready to help. Please reach out at Settings &gt; Help &gt; Contact Support, or say what your issue is and I'll try my best first.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>もちろんです！サポートチームがお手伝いします。設定 &gt; ヘルプ &gt; サポートに連絡からご連絡ください。まず私でお手伝いできることがあればお知らせください。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -894,6 +1064,16 @@
           <t>冗談を教えて</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ha! I wish I could tell jokes, but I'm only trained for app support. I can help with accounts, billing, features, or bugs. What do you need?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>冗談を言えたらいいのですが、アプリサポート専用です！アカウント、請求、機能、バグについてお手伝いできます。何かお困りですか？</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="C28" t="inlineStr">
@@ -906,6 +1086,16 @@
           <t>今何時？</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>I can't tell time, but I can help with your account! Try asking about passwords, subscriptions, billing, or app features.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>時間はわかりませんが、アカウントのお手伝いはできます！パスワード、サブスクリプション、請求、アプリ機能についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
@@ -918,6 +1108,16 @@
           <t>昨日の試合の結果は？</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I don't follow sports, but I'm great at app support! Ask me about your account, billing, features, or report a bug.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>スポーツには詳しくないですが、アプリサポートは得意です！アカウント、請求、機能、バグ報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="C30" t="inlineStr">
@@ -930,6 +1130,16 @@
           <t>ピザを注文して</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>I can't order pizza, but I can help with your app! Try asking about passwords, subscriptions, billing, or features.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ピザの注文はできませんが、アプリのお手伝いならできます！パスワード、サブスクリプション、請求、機能についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -974,6 +1184,16 @@
           <t>やあ</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hi there! Welcome to support. I can help with accounts, billing, subscriptions, app features, and bug reports. What's on your mind?</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>こんにちは！サポートへようこそ。アカウント、請求、サブスクリプション、機能、バグ報告についてお手伝いできます。何かお困りですか？</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="C33" t="inlineStr">
@@ -986,6 +1206,16 @@
           <t>おはようございます</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Hey! I'm your support assistant. Ask me about passwords, billing, subscriptions, features, or report a bug. How can I help?</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>やあ！サポートアシスタントです。パスワード、請求、サブスクリプション、機能、バグ報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="C34" t="inlineStr">
@@ -998,6 +1228,16 @@
           <t>こんばんは</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Hey there! Ready to help. I can assist with accounts, subscriptions, billing, features, and bug reports. What do you need?</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>やあ！お手伝いの準備ができています。アカウント、サブスクリプション、請求、機能、バグ報告について対応できます。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="C35" t="inlineStr">
@@ -1010,6 +1250,16 @@
           <t>すみません</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Of course I can help! I'm your AI support assistant. Ask about passwords, billing, subscriptions, features, or bugs.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>もちろんお手伝いできます！AIサポートアシスタントです。パスワード、請求、サブスクリプション、機能、バグについてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="C36" t="inlineStr">
@@ -1022,6 +1272,16 @@
           <t>助けてください</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hello! I'm here to help. You can ask me about accounts, billing, subscriptions, app features, or report issues.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>こんにちは！お手伝いいたします。アカウント、請求、サブスクリプション、機能、問題報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="C37" t="inlineStr">
@@ -1034,6 +1294,16 @@
           <t>ちょっといいですか</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Good morning! Welcome to support. How can I assist you today? I handle accounts, billing, features, and bug reports.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>おはようございます！サポートへようこそ。今日は何かお手伝いできますか？アカウント、請求、機能、バグ報告に対応しています。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="C38" t="inlineStr">
@@ -1046,6 +1316,16 @@
           <t>よろしくお願いします</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Good afternoon! I'm your support bot. Ask about passwords, subscriptions, billing, or app features. What do you need?</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>こんにちは！サポートボットです。パスワード、サブスクリプション、請求、機能についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="C39" t="inlineStr">
@@ -1058,6 +1338,16 @@
           <t>お世話になります</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Good evening! I'm available 24/7 to help with accounts, billing, subscriptions, and features. What can I help with?</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>こんばんは！アカウント、請求、サブスクリプション、機能について24時間対応しています。何かお手伝いできますか？</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="C40" t="inlineStr">
@@ -1070,6 +1360,16 @@
           <t>手伝ってもらえますか</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Absolutely! I can help with account issues, billing, subscriptions, features, and bug reports. What do you need?</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>もちろんです！アカウント、請求、サブスクリプション、機能、バグ報告についてお手伝いできます。何かお困りですか？</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
@@ -1082,6 +1382,16 @@
           <t>質問があります</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>I'm here to assist! Ask me about passwords, billing, subscriptions, app features, or report a problem.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>お手伝いいたします！パスワード、請求、サブスクリプション、機能、問題報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="C42" t="inlineStr">
@@ -1094,6 +1404,16 @@
           <t>誰かいますか</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes, I'm here! I'm your AI support assistant. How can I help you today?</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>はい、ここにいます！AIサポートアシスタントです。今日は何かお手伝いできますか？</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="C43" t="inlineStr">
@@ -1106,6 +1426,16 @@
           <t>お願いがあります</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>I'm happy to help! What do you need assistance with? I can handle accounts, billing, features, and bugs.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>喜んでお手伝いします！何についてのご質問ですか？アカウント、請求、機能、バグに対応しています。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="C44" t="inlineStr">
@@ -1118,6 +1448,16 @@
           <t>何ができますか</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>I can help with: accounts &amp; passwords, subscriptions, billing, app features, and bug reports. What would you like?</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>お手伝いできること：アカウント・パスワード、サブスクリプション、請求、機能、バグ報告。何をお知りになりたいですか？</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="C45" t="inlineStr">
@@ -1130,6 +1470,16 @@
           <t>聞きたいことがあります</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Great, I'm ready for your question! I handle accounts, billing, subscriptions, features, and technical issues.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ご質問をどうぞ！アカウント、請求、サブスクリプション、機能、技術的な問題に対応しています。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="C46" t="inlineStr">
@@ -1142,6 +1492,16 @@
           <t>ボットさん</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hi! I'm your support bot. Ask me anything about the app — accounts, billing, features, subscriptions, or bugs!</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>こんにちは！サポートボットです。アプリについて何でもお聞きください。アカウント、請求、機能、サブスクリプション、バグなど！</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="C47" t="inlineStr">
@@ -1154,6 +1514,16 @@
           <t>ヘルプ</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>I'm here to help! What do you need? I can assist with accounts, passwords, billing, subscriptions, features, and bugs.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>お手伝いします！何が必要ですか？アカウント、パスワード、請求、サブスクリプション、機能、バグに対応しています。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="C48" t="inlineStr">
@@ -1166,6 +1536,16 @@
           <t>始めましょう</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Let's get started! Tell me what you need help with. I can handle accounts, billing, subscriptions, features, and bugs.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>始めましょう！何についてお手伝いが必要ですか？アカウント、請求、サブスクリプション、機能、バグに対応しています。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="C49" t="inlineStr">
@@ -1178,6 +1558,16 @@
           <t>いますか</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Yes, I'm here! What can I help you with today? Ask about accounts, billing, features, or report a problem.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>はい、ここにいます！今日は何かお手伝いできますか？アカウント、請求、機能、問題報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="C50" t="inlineStr">
@@ -1190,6 +1580,16 @@
           <t>サポートお願いします</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Of course! I'm your support assistant. Ask me about passwords, billing, subscriptions, features, or report issues.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>もちろんです！サポートアシスタントです。パスワード、請求、サブスクリプション、機能、問題報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1212,6 +1612,16 @@
           <t>パスワードが思い出せない</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>That happens! Just tap 'Forgot Password' on the login screen. We'll email you a secure link to create a new password.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>よくあることです！ログイン画面の「パスワードを忘れた」をタップしてください。新しいパスワードを作成するためのリンクをメールでお送りします。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1234,6 +1644,16 @@
           <t>ログインパスワードの変更方法は？</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>To change your login password: Settings &gt; Account &gt; Change Password. You'll need to verify your current password first.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ログインパスワードの変更方法：設定 &gt; アカウント &gt; パスワード変更。まず現在のパスワードの確認が必要です。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1256,6 +1676,16 @@
           <t>パスワードリセットがうまくいかない</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>If the reset isn't working: 1) Check spam folder 2) Make sure the link hasn't expired (30 min) 3) Request a new link. Still stuck? Say 'I need human help'.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>リセットがうまくいかない場合：1) 迷惑メールを確認 2) リンクの有効期限（30分）を確認 3) 新しいリンクをリクエスト。解決しない場合は「人と話したい」とお伝えください。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1278,6 +1708,16 @@
           <t>パスワードを更新したい</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>To update your password: Settings &gt; Account &gt; Change Password. Use at least 8 characters with numbers and symbols for best security.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>パスワードを更新するには：設定 &gt; アカウント &gt; パスワード変更。セキュリティのため、8文字以上で数字と記号を含めてください。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1300,6 +1740,16 @@
           <t>パスワードはどこで変更できますか？</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>You can change your password at: Settings &gt; Account &gt; Change Password. Or use 'Forgot Password' on the login screen.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>パスワードの変更は：設定 &gt; アカウント &gt; パスワード変更。またはログイン画面の「パスワードを忘れた」をご利用ください。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1322,6 +1772,16 @@
           <t>パスワードの有効期限が切れました</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Your password has expired for security. Reset it via Settings &gt; Account &gt; Reset Password, or tap 'Forgot Password' at login.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>セキュリティのためパスワードが期限切れです。設定 &gt; アカウント &gt; パスワードリセット、またはログイン時の「パスワードを忘れた」からリセットしてください。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1344,6 +1804,16 @@
           <t>パスワードを間違えてロックされた</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Account locks happen after multiple failed attempts. Wait 15 minutes and try again, or reset your password via email to unlock immediately.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>複数回のログイン失敗でアカウントがロックされます。15分待って再試行するか、メールでパスワードをリセットして即座に解除できます。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1366,6 +1836,16 @@
           <t>パスワードエラーが出続けます</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Password errors usually mean it's incorrect or expired. Try 'Forgot Password' on the login screen to create a new one.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>パスワードエラーは通常、パスワードが間違っているか期限切れです。ログイン画面の「パスワードを忘れた」から新しいパスワードを作成してください。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1388,6 +1868,16 @@
           <t>アカウントに戻れるようにして</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Let's get you back in! Go to the login screen &gt; tap 'Forgot Password' &gt; enter your email. A recovery link will arrive within minutes.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>アカウントに戻れるようお手伝いします！ログイン画面 &gt; 「パスワードを忘れた」&gt; メールアドレスを入力。数分以内に復旧リンクが届きます。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1410,6 +1900,16 @@
           <t>ログイン情報を変更したい</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>To change your login info: Settings &gt; Account &gt; Change Password. You'll need your current password for verification.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ログイン情報の変更：設定 &gt; アカウント &gt; パスワード変更。確認のため現在のパスワードが必要です。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1432,6 +1932,16 @@
           <t>認証情報を忘れました</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>No problem! Tap 'Forgot Password' on the login screen and enter your registered email. We'll send a reset link right away.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>大丈夫です！ログイン画面の「パスワードを忘れた」をタップし、登録メールアドレスを入力してください。リセットリンクをすぐにお送りします。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1454,6 +1964,16 @@
           <t>新しいパスワードを設定するには</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>To set a new password: Settings &gt; Account &gt; Change Password. Choose at least 8 characters with mixed case, numbers, and symbols.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>新しいパスワードの設定：設定 &gt; アカウント &gt; パスワード変更。8文字以上で大小文字・数字・記号を含めてください。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1476,6 +1996,16 @@
           <t>サービスの支払いを止めたい</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>To stop paying: Settings &gt; Subscription &gt; Cancel Plan. You won't be charged again after your current billing period ends.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>支払いを停止するには：設定 &gt; サブスクリプション &gt; キャンセル。現在の請求期間終了後は課金されません。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1498,6 +2028,16 @@
           <t>会員を解約するには？</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>To end your membership: Settings &gt; Subscription &gt; Cancel Plan. Your access continues until the billing period ends.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>メンバーシップを終了するには：設定 &gt; サブスクリプション &gt; キャンセル。請求期間終了までアクセスは継続されます。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1520,6 +2060,16 @@
           <t>アカウントのサブスクをキャンセルしたい</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>To cancel: Settings &gt; Subscription &gt; Cancel Plan. Follow the confirmation steps and you're all set.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>キャンセルするには：設定 &gt; サブスクリプション &gt; キャンセル。確認手順に従えば完了です。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1542,6 +2092,16 @@
           <t>更新したくありません</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>To stop renewal: Settings &gt; Subscription &gt; Cancel Plan. Your plan won't auto-renew and you keep access until the current period ends.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>自動更新を停止するには：設定 &gt; サブスクリプション &gt; キャンセル。自動更新が停止され、現在の期間終了まで利用できます。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1564,6 +2124,16 @@
           <t>月額課金を止めてください</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>To stop monthly payments: Settings &gt; Subscription &gt; Cancel Plan. No more charges after the current cycle ends.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>月額支払いを停止するには：設定 &gt; サブスクリプション &gt; キャンセル。現在の期間終了後は課金されません。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1586,6 +2156,16 @@
           <t>プランのキャンセルはどこで？</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>You can cancel at: Settings &gt; Subscription &gt; Cancel Plan. The process takes less than a minute.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>キャンセルは：設定 &gt; サブスクリプション &gt; キャンセル から行えます。1分もかかりません。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1608,6 +2188,16 @@
           <t>無料プランに戻したい</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>To downgrade to free: Settings &gt; Subscription &gt; Change Plan &gt; Free. You'll keep your data and basic features.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>無料プランへダウングレード：設定 &gt; サブスクリプション &gt; プラン変更 &gt; 無料。データと基本機能はそのまま保持されます。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1630,6 +2220,16 @@
           <t>プレミアムの登録を終了したい</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>To end premium: Settings &gt; Subscription &gt; Cancel Plan. You'll switch to the free plan after your current period ends.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>プレミアムを終了するには：設定 &gt; サブスクリプション &gt; キャンセル。現在の期間終了後に無料プランに切り替わります。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1652,6 +2252,16 @@
           <t>サブスクリプションを解除したい</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>To remove your subscription: Settings &gt; Subscription &gt; Cancel Plan. Confirmation email will be sent to you.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>サブスクリプションを解除するには：設定 &gt; サブスクリプション &gt; キャンセル。確認メールが送信されます。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1674,6 +2284,16 @@
           <t>このサービスはもう不要です</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>To cancel since you no longer need the service: Settings &gt; Subscription &gt; Cancel Plan. We're sorry to see you go!</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>サービスが不要になった場合のキャンセル：設定 &gt; サブスクリプション &gt; キャンセル。ご利用ありがとうございました！</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1696,6 +2316,16 @@
           <t>すべての登録を解除して</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>To unsubscribe from everything: Settings &gt; Subscription &gt; Cancel Plan. For email notifications, also check Settings &gt; Notifications.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>すべての解約：設定 &gt; サブスクリプション &gt; キャンセル。メール通知については設定 &gt; 通知もご確認ください。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1718,6 +2348,16 @@
           <t>更新をキャンセルしてください</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>To cancel renewal: Settings &gt; Subscription &gt; Cancel Plan. Your plan won't renew and access continues until the end of the current period.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>更新をキャンセルするには：設定 &gt; サブスクリプション &gt; キャンセル。更新されず、現在の期間終了までアクセスは継続されます。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1740,6 +2380,16 @@
           <t>予期しない請求があります</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Unexpected charges may be from a plan upgrade or trial ending. Check Settings &gt; Billing for details. If it's an error, we can process a refund within 14 days.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>予期しない請求はプランのアップグレードやトライアル終了の可能性があります。設定 &gt; 請求で詳細を確認してください。誤りの場合は14日以内に返金処理が可能です。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1762,6 +2412,16 @@
           <t>請求書はどこで確認できますか？</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>View your invoices at: Settings &gt; Billing &gt; Invoice History. You can download PDFs for each billing period.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>請求書の確認：設定 &gt; 請求 &gt; 請求履歴。各請求期間のPDFをダウンロードできます。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1784,6 +2444,16 @@
           <t>過剰請求されました</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sorry about the overcharge! Check Settings &gt; Billing for payment details. If it's incorrect, we can issue a refund within 14 days. Say 'I need human help' for urgent cases.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>過大請求について申し訳ございません！設定 &gt; 請求で支払い詳細をご確認ください。誤りの場合は14日以内に返金いたします。緊急の場合は「人と話したい」とお伝えください。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1806,6 +2476,16 @@
           <t>次の請求日はいつですか？</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Your next billing date is shown at Settings &gt; Billing &gt; Subscription Details. You'll also receive an email reminder 3 days before.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>次回の請求日は設定 &gt; 請求 &gt; サブスクリプション詳細に表示されています。請求日の3日前にメールでもお知らせします。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1828,6 +2508,16 @@
           <t>返金してもらえますか？</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Refunds can be processed within 14 days of purchase. Go to Settings &gt; Billing &gt; select the transaction &gt; Request Refund. Or say 'I need human help' for assistance.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>購入から14日以内であれば返金可能です。設定 &gt; 請求 &gt; 該当取引を選択 &gt; 返金リクエスト。サポートが必要な場合は「人と話したい」とお伝えください。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1850,6 +2540,16 @@
           <t>年間払いに変更するには？</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>To switch to annual billing: Settings &gt; Billing &gt; Change Plan &gt; Annual. You'll save up to 20% compared to monthly!</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>年額課金への切り替え：設定 &gt; 請求 &gt; プラン変更 &gt; 年額。月額と比べて最大20%お得です！</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1872,6 +2572,16 @@
           <t>クレジットカードが拒否されました</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>If your card was declined: 1) Verify card details are correct 2) Check with your bank 3) Try a different payment method at Settings &gt; Billing &gt; Payment Methods.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>カードが拒否された場合：1) カード情報が正しいか確認 2) 銀行にお問い合わせ 3) 設定 &gt; 請求 &gt; 支払い方法で別の方法をお試しください。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1894,6 +2604,16 @@
           <t>プレミアムプランはいくらですか？</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Premium plan pricing is shown at Settings &gt; Subscription &gt; View Plans. We offer monthly and annual options with different features.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>プレミアムプランの価格は設定 &gt; サブスクリプション &gt; プラン一覧でご確認いただけます。月額と年額のオプションがあります。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1916,6 +2636,16 @@
           <t>請求先住所を変更したい</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>To change billing address: Settings &gt; Billing &gt; Billing Address &gt; Edit. Update your address and save.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>請求先住所の変更：設定 &gt; 請求 &gt; 請求先住所 &gt; 編集。住所を更新して保存してください。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1938,6 +2668,16 @@
           <t>支払い失敗なのにお金が引かれた</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>If payment failed but money was taken, it usually resolves within 3-5 business days. If not, contact your bank or say 'I need human help' for immediate assistance.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>支払い失敗でお金が引かれた場合、通常3〜5営業日以内に解決します。解決しない場合は銀行にお問い合わせいただくか、「人と話したい」とお伝えください。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1960,6 +2700,16 @@
           <t>プロモーションコードの適用方法は？</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>To apply a promo code: Settings &gt; Billing &gt; Apply Promo Code. Enter the code and tap Apply. Discount will be applied to your next billing.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>プロモコードの適用：設定 &gt; 請求 &gt; プロモコード適用。コードを入力して適用をタップ。割引は次回の請求に反映されます。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1982,6 +2732,16 @@
           <t>明細付きの領収書が必要です</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Itemized receipts are available at Settings &gt; Billing &gt; Invoice History. Select any transaction and tap 'Download Detailed Receipt'.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>明細付き領収書は設定 &gt; 請求 &gt; 請求履歴からご利用いただけます。取引を選択し「詳細領収書をダウンロード」をタップしてください。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2004,6 +2764,16 @@
           <t>通知を有効にするには？</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>To enable notifications: Settings &gt; Notifications &gt; toggle on. You can customize which notifications you receive.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>通知を有効にするには：設定 &gt; 通知 &gt; オンに切り替え。受け取る通知の種類をカスタマイズできます。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2026,6 +2796,16 @@
           <t>設定はどこですか？</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Settings can be found by tapping the gear icon in the top-right corner of the home screen, or via the menu &gt; Settings.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>設定はホーム画面右上の歯車アイコンをタップするか、メニュー &gt; 設定からアクセスできます。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2048,6 +2828,16 @@
           <t>データをエクスポートするには？</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>To export your data: Settings &gt; Privacy &gt; Export Data. You'll receive a download link via email within 24 hours.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>データのエクスポート：設定 &gt; プライバシー &gt; データエクスポート。24時間以内にメールでダウンロードリンクが届きます。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2070,6 +2860,16 @@
           <t>オフラインモードは使えますか？</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yes! To use offline mode: Settings &gt; General &gt; Offline Mode. Downloaded content will be available without internet.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>はい！オフラインモードの利用：設定 &gt; 一般 &gt; オフラインモード。ダウンロード済みコンテンツがインターネットなしで利用可能です。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2092,6 +2892,16 @@
           <t>言語を変更するには？</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>To change language: Settings &gt; General &gt; Language. Select your preferred language and restart the app.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>言語の変更：設定 &gt; 一般 &gt; 言語。希望する言語を選択してアプリを再起動してください。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2114,6 +2924,16 @@
           <t>プロフィールを共有するには？</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>To share your profile: go to your Profile page &gt; tap the Share icon (top-right). You can copy the link or share directly.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>プロフィールの共有：プロフィールページ &gt; 共有アイコン（右上）をタップ。リンクをコピーするか直接共有できます。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2136,6 +2956,16 @@
           <t>検索機能はありますか？</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes! Tap the search icon (magnifying glass) at the top of any screen. You can search content, settings, and help articles.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>はい！画面上部の検索アイコン（虫眼鏡）をタップしてください。コンテンツ、設定、ヘルプ記事を検索できます。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2158,6 +2988,16 @@
           <t>履歴を削除するには？</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>To delete history: Settings &gt; Privacy &gt; Clear History. You can choose to clear all or select specific items.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>履歴の削除：設定 &gt; プライバシー &gt; 履歴を消去。すべて消去するか、特定の項目を選択できます。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2180,6 +3020,16 @@
           <t>デバイス間で同期できますか？</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes! Sign in with the same account on multiple devices. Your data syncs automatically via Settings &gt; Account &gt; Sync.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>はい！複数のデバイスで同じアカウントにログインしてください。設定 &gt; アカウント &gt; 同期でデータが自動同期されます。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2202,6 +3052,16 @@
           <t>二段階認証の設定方法は？</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>To set up 2FA: Settings &gt; Security &gt; Two-Factor Authentication &gt; Enable. You'll need an authenticator app like Google Authenticator.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>二段階認証の設定：設定 &gt; セキュリティ &gt; 二段階認証 &gt; 有効化。Google Authenticatorなどの認証アプリが必要です。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2224,6 +3084,16 @@
           <t>ダッシュボードをカスタマイズするには？</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>To customize your dashboard: Home &gt; tap Edit (pencil icon). Drag widgets to rearrange, and toggle visibility on/off.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ダッシュボードのカスタマイズ：ホーム &gt; 編集（鉛筆アイコン）をタップ。ウィジェットをドラッグして並べ替え、表示/非表示を切り替えられます。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2246,6 +3116,16 @@
           <t>ユーザー名を変更できますか？</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>To change username: Settings &gt; Account &gt; Edit Profile &gt; Username. Note: you can only change it once every 30 days.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ユーザー名の変更：設定 &gt; アカウント &gt; プロフィール編集 &gt; ユーザー名。注意：変更は30日に1回のみ可能です。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2268,6 +3148,16 @@
           <t>設定を開くと画面が真っ白になる</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>We're aware of display issues in settings. Try: 1) Clear app cache 2) Update to the latest version. Report at Settings &gt; Help &gt; Report a Bug with your device model.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>設定画面の表示問題を認識しています。お試しください：1) アプリキャッシュを消去 2) 最新版にアップデート。デバイスモデルを添えて設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2290,6 +3180,16 @@
           <t>ロード画面でフリーズする</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Loading screen freeze: try force closing and reopening the app. If it continues, clear the app cache or reinstall. Report at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ロード画面のフリーズ：アプリを強制終了して再起動してください。続く場合はキャッシュの消去または再インストールをお試しください。設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2312,6 +3212,16 @@
           <t>エラーメッセージが出続けます</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Error messages can mean many things. Please note the exact error code/text and report it at Settings &gt; Help &gt; Report a Bug. We'll investigate ASAP.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>エラーメッセージにはさまざまな原因があります。正確なエラーコード/テキストをメモして設定 &gt; ヘルプ &gt; バグを報告からご連絡ください。早急に調査します。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2334,6 +3244,16 @@
           <t>ログインするたびにアプリが落ちる</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Login crashes: 1) Clear app cache 2) Check for updates 3) Try uninstalling and reinstalling. If it persists, report with device model at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ログイン時のクラッシュ：1) キャッシュ消去 2) アップデートを確認 3) アプリの再インストール。改善しない場合はデバイスモデルを添えて設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2356,6 +3276,16 @@
           <t>ボタンが反応しない</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Unresponsive buttons: try scrolling to refresh the page, or force close and reopen the app. Report at Settings &gt; Help &gt; Report a Bug with your OS version.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ボタンが反応しない場合：ページをスクロールして更新するか、アプリを強制終了して再起動してください。OSバージョンを添えて設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2378,6 +3308,16 @@
           <t>ページが正しく表示されない</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Page loading issues: check your internet connection first. Then try: 1) Clear app cache 2) Update the app. Report at Settings &gt; Help &gt; Report a Bug if it continues.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ページの読み込み問題：まずインターネット接続を確認。次に：1) キャッシュ消去 2) アプリ更新。続く場合は設定 &gt; ヘルプ &gt; バグを報告からご連絡ください。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2400,6 +3340,16 @@
           <t>アップデート後にデータが消えた</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>We're sorry about the data loss! Please report immediately at Settings &gt; Help &gt; Report a Bug. Our team may be able to recover your data. Say 'I need human help' for urgent assistance.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>データの消失について大変申し訳ございません！すぐに設定 &gt; ヘルプ &gt; バグを報告からご連絡ください。データの復旧が可能な場合があります。緊急の場合は「人と話したい」とお伝えください。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2422,6 +3372,16 @@
           <t>表示にバグがあります</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Display glitches: try 1) Rotating your screen 2) Restarting the app 3) Updating to the latest version. Report with a screenshot at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>表示の不具合：お試しください 1) 画面を回転 2) アプリを再起動 3) 最新版にアップデート。スクリーンショットを添えて設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2444,6 +3404,16 @@
           <t>通知が届かなくなった</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Notification issues: check Settings &gt; Notifications are enabled, and verify your device allows notifications for our app. Try toggling off and on.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>通知の問題：設定 &gt; 通知が有効になっているか確認し、デバイスのアプリ通知許可も確認してください。オフにしてからオンに切り替えてみてください。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2466,6 +3436,16 @@
           <t>検索結果がおかしい</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Wrong search results: this may be a cache issue. Try clearing app cache at Settings &gt; General &gt; Clear Cache. If it persists, report at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>検索結果の誤り：キャッシュの問題の可能性があります。設定 &gt; 一般 &gt; キャッシュ消去をお試しください。改善しない場合は設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2488,6 +3468,16 @@
           <t>アプリで動画が再生されない</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Video playback issues: 1) Check internet connection 2) Try switching between Wi-Fi and mobile data 3) Clear app cache. Report at Settings &gt; Help &gt; Report a Bug.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>動画再生の問題：1) インターネット接続を確認 2) Wi-Fiとモバイルデータを切り替え 3) キャッシュ消去。設定 &gt; ヘルプ &gt; バグを報告からご連絡ください。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2510,6 +3500,16 @@
           <t>保存しようとするとエラーが出る</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Save errors: try 1) Check you have enough storage 2) Force close and retry 3) Check for app updates. Report at Settings &gt; Help &gt; Report a Bug with the error details.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>保存エラー：お試しください 1) ストレージの空き容量を確認 2) 強制終了して再試行 3) アプリの更新を確認。エラー詳細を添えて設定 &gt; ヘルプ &gt; バグを報告へ。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2532,6 +3532,16 @@
           <t>マネージャーと話させてください</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>I understand your frustration. I'll escalate this to a senior team member. Please submit details at Settings &gt; Help &gt; Contact Support and mark it as urgent.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ご不満をお察しします。上級チームメンバーにエスカレートいたします。設定 &gt; ヘルプ &gt; サポートに連絡から詳細を送信し、緊急としてマークしてください。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2554,6 +3564,16 @@
           <t>苦情を申し立てたい</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>I'm sorry you're having trouble. To file a complaint: Settings &gt; Help &gt; Contact Support &gt; select 'Complaint'. We take all feedback seriously.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ご迷惑をおかけして申し訳ございません。苦情を提出するには：設定 &gt; ヘルプ &gt; サポートに連絡 &gt; 「苦情」を選択。すべてのフィードバックを真摯に受け止めています。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2576,6 +3596,16 @@
           <t>このボットでは解決できません</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>I understand! Let me connect you with our team. Please reach out at Settings &gt; Help &gt; Contact Support for personalized help within 24 hours.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>かしこまりました！チームにおつなぎします。設定 &gt; ヘルプ &gt; サポートに連絡から、24時間以内に個別対応いたします。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2598,6 +3628,16 @@
           <t>人間のオペレーターに転送して</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Transferring you! Please contact our team at Settings &gt; Help &gt; Contact Support. Include your account email for faster service.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>おつなぎします！設定 &gt; ヘルプ &gt; サポートに連絡からチームにご連絡ください。アカウントメールを記載いただくと迅速に対応できます。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2620,6 +3660,16 @@
           <t>本物の人と話す必要があります</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Of course! Our team is available at Settings &gt; Help &gt; Contact Support. Response time is within 24 hours, urgent issues are prioritized.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>もちろんです！設定 &gt; ヘルプ &gt; サポートに連絡からチームにご連絡いただけます。24時間以内に対応し、緊急の問題は優先されます。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2642,6 +3692,16 @@
           <t>カスタマーサービスに電話できますか？</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Phone support is available Mon-Fri 9AM-6PM (JST). You can also reach us via Settings &gt; Help &gt; Contact Support for 24/7 chat assistance.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>電話サポートは月〜金 9:00-18:00（JST）で対応しています。設定 &gt; ヘルプ &gt; サポートに連絡から24時間チャットもご利用いただけます。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2664,6 +3724,16 @@
           <t>折り返し電話がほしい</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>We can arrange a callback! Please submit your request at Settings &gt; Help &gt; Contact Support &gt; select 'Request Callback'. Include your phone number and preferred time.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>コールバックを手配できます！設定 &gt; ヘルプ &gt; サポートに連絡 &gt; 「コールバックリクエスト」を選択。電話番号とご希望の時間をお知らせください。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2686,6 +3756,16 @@
           <t>問題をエスカレートしてください</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>I'll escalate your issue right away. Please provide details at Settings &gt; Help &gt; Contact Support and mark the priority as 'High'.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>すぐに問題をエスカレートします。設定 &gt; ヘルプ &gt; サポートに連絡で詳細をお知らせいただき、優先度を「高」に設定してください。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2708,6 +3788,16 @@
           <t>ライブチャットはありますか？</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Yes! Live chat is available at Settings &gt; Help &gt; Live Chat during business hours (Mon-Fri 9AM-6PM JST). Outside hours, use Contact Support for async help.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>はい！ライブチャットは営業時間中（月〜金 9:00-18:00 JST）に設定 &gt; ヘルプ &gt; ライブチャットからご利用いただけます。営業時間外はサポートに連絡をご利用ください。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2730,6 +3820,16 @@
           <t>ボットでは対応できない問題です</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>I understand — some issues need a personal touch. Please describe your situation at Settings &gt; Help &gt; Contact Support. Our experts will handle it.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>かしこまりました。個別対応が必要な問題もございます。設定 &gt; ヘルプ &gt; サポートに連絡で状況をお知らせください。専門スタッフが対応いたします。</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2752,6 +3852,16 @@
           <t>実際のスタッフにつないでください</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Connecting you with a real agent! Please submit your request at Settings &gt; Help &gt; Contact Support. Include your issue summary for faster help.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>実際のエージェントにおつなぎします！設定 &gt; ヘルプ &gt; サポートに連絡からリクエストを送信してください。問題の概要を記載いただくと迅速に対応できます。</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2774,6 +3884,16 @@
           <t>個別のサポートが必要です</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Of course! For personalized assistance, reach our team at Settings &gt; Help &gt; Contact Support. They'll work with you one-on-one to resolve your issue.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>もちろんです！個別対応は設定 &gt; ヘルプ &gt; サポートに連絡からチームにご連絡ください。マンツーマンで問題解決にあたります。</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2796,6 +3916,16 @@
           <t>フランスの首都はどこ？</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Geography isn't my specialty — app support is! Ask me about accounts, subscriptions, billing, features, or bugs.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>地理は専門外ですが、アプリサポートなら任せてください！アカウント、サブスクリプション、請求、機能、バグについてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2818,6 +3948,16 @@
           <t>音楽を再生して</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>I can't play music, but I can help with your app experience! What do you need help with?</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>音楽は再生できませんが、アプリのご利用についてお手伝いできます！何かお困りですか？</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2840,6 +3980,16 @@
           <t>今日の株式市場はどう？</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Stock market isn't my area — I'm here for app support! Ask about accounts, billing, features, or report issues.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>株式市場は専門外です。アプリサポートならお任せください！アカウント、請求、機能、問題報告についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2862,6 +4012,16 @@
           <t>エッセイを書いて</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Essay writing is beyond my abilities! But I'm great at helping with your app. What can I assist you with?</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>エッセイの作成はできませんが、アプリのお手伝いなら得意です！何かお手伝いできることはありますか？</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2884,6 +4044,16 @@
           <t>これをスペイン語に翻訳して</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>I can't translate, but I can help in both English and Japanese for app support! What do you need?</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>翻訳はできませんが、アプリサポートは英語と日本語の両方で対応できます！何かお困りですか？</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2906,6 +4076,16 @@
           <t>飛行機を予約して</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>I can't book flights, but I can help with your app account, subscription, billing, or features!</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>航空券の予約はできませんが、アプリのアカウント、サブスクリプション、請求、機能についてお手伝いできます！</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2928,6 +4108,16 @@
           <t>2+2は？</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Math isn't my thing — app support is! Ask me about passwords, subscriptions, billing, or app features.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>計算は専門外です。アプリサポートならお任せください！パスワード、サブスクリプション、請求、機能についてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2950,6 +4140,16 @@
           <t>午前7時にアラームをセットして</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>I can't set alarms, but I can help you get the most out of your app! What would you like to know?</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>アラームは設定できませんが、アプリの活用方法ならお手伝いできます！何をお知りになりたいですか？</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2972,6 +4172,16 @@
           <t>大統領は誰？</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>I don't follow politics, but I'm an expert at app support! Ask about accounts, billing, features, or bugs.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>政治には詳しくないですが、アプリサポートなら専門家です！アカウント、請求、機能、バグについてお聞きください。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2992,6 +4202,16 @@
       <c r="D132" t="inlineStr">
         <is>
           <t>近くのレストランを探して</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>I can't find restaurants, but I can navigate your app! Ask about settings, features, account, or billing.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>レストラン検索はできませんが、アプリのナビゲートならお任せください！設定、機能、アカウント、請求についてお聞きください。</t>
         </is>
       </c>
     </row>
